--- a/www/terminologies/CodeSystem-TRE-R274-ActiviteSanitaireRegulee.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R274-ActiviteSanitaireRegulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="219">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20260827120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2026-08-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>66</t>
+    <t>78</t>
   </si>
   <si>
     <t>Code</t>
@@ -457,6 +457,72 @@
     <t>Prélèvement de tissus</t>
   </si>
   <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>Greffe de face ou de face inférieure</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de main</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées autologues</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées allogéniques</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale d'avant-bras</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de bras</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Greffe de membre inférieur</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Greffe de langue</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Greffe de pénis</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Greffe de paroi abdominale</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Greffe de tissus cutanés conjonctifs et vasculo- nerveux</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
@@ -551,6 +617,12 @@
   </si>
   <si>
     <t>Prise en charge des patients atteints de sclérose en plaques</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>Maison de naissance</t>
   </si>
   <si>
     <t>T0</t>
@@ -1016,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1825,6 +1897,150 @@
       </c>
       <c r="D67" s="2"/>
     </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
